--- a/output/pdf_financials_xlsx/CMET.xlsx
+++ b/output/pdf_financials_xlsx/CMET.xlsx
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.178662</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.396065</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.422122</v>
       </c>
     </row>
     <row r="93">
@@ -2974,7 +2974,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>0.178662</v>
       </c>

--- a/output/pdf_financials_xlsx/CMET.xlsx
+++ b/output/pdf_financials_xlsx/CMET.xlsx
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.02056</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.00423</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.407713</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.02056</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.00423</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.407713</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.052483</v>
+        <v>0.031923</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.00423</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.407713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/CMET.xlsx
+++ b/output/pdf_financials_xlsx/CMET.xlsx
@@ -1515,10 +1515,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.065862</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.087698</v>
       </c>
     </row>
     <row r="68">
@@ -3468,7 +3468,11 @@
           <t>Private Placement</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
